--- a/Parametros.xlsx
+++ b/Parametros.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Python\Cotizador Tola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B871FB26-74D2-4E51-8AE1-812314A050DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62052A82-7E0E-412E-8AA6-FF7FF2DB555F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A452CBD-4F16-48E8-B738-B8114C600522}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cajas de Vino" sheetId="1" r:id="rId1"/>
-    <sheet name="Logos" sheetId="2" r:id="rId2"/>
+    <sheet name="Precios" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,11 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Tipo Material Tapa</t>
   </si>
   <si>
+    <t>Tipo de Caja</t>
+  </si>
+  <si>
     <t>Precio</t>
   </si>
   <si>
@@ -79,13 +81,16 @@
     <t>Concepto</t>
   </si>
   <si>
+    <t>Factor</t>
+  </si>
+  <si>
     <t>1mm2</t>
   </si>
   <si>
+    <t>Cantidad de logos</t>
+  </si>
+  <si>
     <t xml:space="preserve">const Precio_Logo </t>
-  </si>
-  <si>
-    <t>Medida Caja</t>
   </si>
 </sst>
 </file>
@@ -93,9 +98,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -132,13 +137,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -146,7 +151,7 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;????_-;_-@_-"/>
+      <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;????_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -165,7 +170,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -185,7 +190,7 @@
   <autoFilter ref="B2:D14" xr:uid="{C801491E-5388-4D89-A438-C6363EF23ECD}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{78FCC551-4A17-46D6-9535-76EA70805BFB}" name="Tipo Material Tapa"/>
-    <tableColumn id="2" xr3:uid="{E3B3F35E-82B8-4B08-9E3F-AA55A6FBC3C4}" name="Medida Caja"/>
+    <tableColumn id="2" xr3:uid="{E3B3F35E-82B8-4B08-9E3F-AA55A6FBC3C4}" name="Tipo de Caja"/>
     <tableColumn id="3" xr3:uid="{A8CB473E-5D57-4C59-8AFA-49455AC9BB39}" name="Precio" dataCellStyle="Moneda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -193,14 +198,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4FD14101-FE95-4EA0-BC3C-92E6367AF093}" name="Logos" displayName="Logos" ref="C2:E3" totalsRowShown="0">
-  <autoFilter ref="C2:E3" xr:uid="{4FD14101-FE95-4EA0-BC3C-92E6367AF093}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4FD14101-FE95-4EA0-BC3C-92E6367AF093}" name="Logos" displayName="Logos" ref="C16:E17" totalsRowShown="0">
+  <autoFilter ref="C16:E17" xr:uid="{4FD14101-FE95-4EA0-BC3C-92E6367AF093}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F7551A99-7AA6-4D45-AE14-53A7FFED83E8}" name="Concepto"/>
     <tableColumn id="2" xr3:uid="{F620C6E1-8F17-439E-B1F1-A2D482276749}" name="Marce" dataDxfId="1" dataCellStyle="Moneda"/>
     <tableColumn id="3" xr3:uid="{53A38C65-E8D0-4EE2-B14F-1E7AB7BC42E9}" name="Clientes" dataDxfId="0">
-      <calculatedColumnFormula>D3*1.1</calculatedColumnFormula>
+      <calculatedColumnFormula>D17*1.1</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AA1B36F9-51D9-4700-8E87-B8A61B080CCB}" name="Escalas" displayName="Escalas" ref="B19:C27" totalsRowShown="0">
+  <autoFilter ref="B19:C27" xr:uid="{AA1B36F9-51D9-4700-8E87-B8A61B080CCB}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9A01F8C4-B6F0-480F-84D3-5D74383B0036}" name="Cantidad de logos"/>
+    <tableColumn id="2" xr3:uid="{1CF945CB-7D10-4A40-8348-377A36E0B400}" name="Factor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -503,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A851CE1-EB60-43A1-8B98-1725BEBB5F2F}">
-  <dimension ref="B2:D14"/>
+  <dimension ref="B2:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -515,192 +531,253 @@
     <col min="9" max="9" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>4320</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
         <v>7513</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1">
         <v>3927</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
         <v>4485</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1">
         <v>6830</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1">
         <v>9280</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1">
         <v>11590</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1">
         <v>14641</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>17383</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1">
         <v>6485</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1">
         <v>9350</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1">
         <v>8640</v>
       </c>
     </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.41760000000000003</v>
+      </c>
+      <c r="E17" s="3">
+        <f>D17*1.1</f>
+        <v>0.45936000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>500</v>
+      </c>
+      <c r="C25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>1000</v>
+      </c>
+      <c r="C26">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>9999999</v>
+      </c>
+      <c r="C27">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9150BEA7-B763-4502-84E5-903CE8F164CF}">
-  <dimension ref="B2:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="E3" s="3">
-        <f>D3*1.1</f>
-        <v>0.38940000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>